--- a/Data/BUS/Cost_index_18.xlsx
+++ b/Data/BUS/Cost_index_18.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.803017393925831</v>
+        <v>1.841896475196469</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.985425380423761</v>
+        <v>3.075892816194178</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.009912170129032</v>
+        <v>4.273722181321732</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.132090715149524</v>
+        <v>5.492940843558475</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.899651856821434</v>
+        <v>1.972499863130221</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.86375597876756</v>
+        <v>5.070724318289583</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.668522429361305</v>
+        <v>3.781400042572422</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.06660327438749</v>
+        <v>2.125092046304117</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.386211722433925</v>
+        <v>2.588575967445989</v>
       </c>
     </row>
     <row r="11">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.151081432230348</v>
+        <v>2.164483808755148</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.870867532897345</v>
+        <v>2.953228486709973</v>
       </c>
     </row>
     <row r="13">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.759713631961706</v>
+        <v>1.782158958899993</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.496811557006461</v>
+        <v>3.696629360263973</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.193817845881633</v>
+        <v>2.247986187755254</v>
       </c>
     </row>
     <row r="16">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.263796980858579</v>
+        <v>5.55856961178666</v>
       </c>
     </row>
     <row r="17">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.900086003063347</v>
+        <v>2.010924353242042</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.995987652267479</v>
+        <v>2.126160760024053</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.118837891360352</v>
+        <v>3.190044235911958</v>
       </c>
     </row>
   </sheetData>

--- a/Data/BUS/Cost_index_18.xlsx
+++ b/Data/BUS/Cost_index_18.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.841896475196469</v>
+        <v>1.84930949412904</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.075892816194178</v>
+        <v>3.075867121037544</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.273722181321732</v>
+        <v>4.27639364943454</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.492940843558475</v>
+        <v>5.49274023187377</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.972499863130221</v>
+        <v>1.978903614925749</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.070724318289583</v>
+        <v>5.082911944550688</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.781400042572422</v>
+        <v>3.818203773844363</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.125092046304117</v>
+        <v>2.114631448180023</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.588575967445989</v>
+        <v>2.585819340022317</v>
       </c>
     </row>
     <row r="11">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.164483808755148</v>
+        <v>2.169578909493137</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.953228486709973</v>
+        <v>2.955856734516588</v>
       </c>
     </row>
     <row r="13">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.782158958899993</v>
+        <v>1.776562611907709</v>
       </c>
     </row>
     <row r="14">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.696629360263973</v>
+        <v>3.694651283975074</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.247986187755254</v>
+        <v>2.218062621383034</v>
       </c>
     </row>
     <row r="16">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.55856961178666</v>
+        <v>5.574087662420545</v>
       </c>
     </row>
     <row r="17">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.010924353242042</v>
+        <v>2.010126630445508</v>
       </c>
     </row>
     <row r="18">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.126160760024053</v>
+        <v>2.117823541057404</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.190044235911958</v>
+        <v>3.17919440991437</v>
       </c>
     </row>
   </sheetData>

--- a/Data/BUS/Cost_index_18.xlsx
+++ b/Data/BUS/Cost_index_18.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Data/BUS/Cost_index_18.xlsx
+++ b/Data/BUS/Cost_index_18.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>MEAN_COST_INDEX(%)</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>NUMBER_ROUTES</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -452,6 +457,9 @@
       <c r="C2" t="n">
         <v>1.84930949412904</v>
       </c>
+      <c r="D2" t="n">
+        <v>371</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -465,6 +473,9 @@
       <c r="C3" t="n">
         <v>3.075867121037544</v>
       </c>
+      <c r="D3" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -478,6 +489,9 @@
       <c r="C4" t="n">
         <v>4.27639364943454</v>
       </c>
+      <c r="D4" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -491,6 +505,9 @@
       <c r="C5" t="n">
         <v>5.49274023187377</v>
       </c>
+      <c r="D5" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -504,6 +521,9 @@
       <c r="C6" t="n">
         <v>1.978903614925749</v>
       </c>
+      <c r="D6" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -517,6 +537,9 @@
       <c r="C7" t="n">
         <v>5.082911944550688</v>
       </c>
+      <c r="D7" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -530,6 +553,9 @@
       <c r="C8" t="n">
         <v>3.818203773844363</v>
       </c>
+      <c r="D8" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -543,6 +569,9 @@
       <c r="C9" t="n">
         <v>2.114631448180023</v>
       </c>
+      <c r="D9" t="n">
+        <v>318</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -556,6 +585,9 @@
       <c r="C10" t="n">
         <v>2.585819340022317</v>
       </c>
+      <c r="D10" t="n">
+        <v>283</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -569,6 +601,9 @@
       <c r="C11" t="n">
         <v>2.169578909493137</v>
       </c>
+      <c r="D11" t="n">
+        <v>321</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -582,6 +617,9 @@
       <c r="C12" t="n">
         <v>2.955856734516588</v>
       </c>
+      <c r="D12" t="n">
+        <v>244</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -595,6 +633,9 @@
       <c r="C13" t="n">
         <v>1.776562611907709</v>
       </c>
+      <c r="D13" t="n">
+        <v>392</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -608,6 +649,9 @@
       <c r="C14" t="n">
         <v>3.694651283975074</v>
       </c>
+      <c r="D14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -621,6 +665,9 @@
       <c r="C15" t="n">
         <v>2.218062621383034</v>
       </c>
+      <c r="D15" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -634,6 +681,9 @@
       <c r="C16" t="n">
         <v>5.574087662420545</v>
       </c>
+      <c r="D16" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -647,6 +697,9 @@
       <c r="C17" t="n">
         <v>2.010126630445508</v>
       </c>
+      <c r="D17" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -660,6 +713,9 @@
       <c r="C18" t="n">
         <v>2.117823541057404</v>
       </c>
+      <c r="D18" t="n">
+        <v>276</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -672,6 +728,9 @@
       </c>
       <c r="C19" t="n">
         <v>3.17919440991437</v>
+      </c>
+      <c r="D19" t="n">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
